--- a/reports/model_comparison.xlsx
+++ b/reports/model_comparison.xlsx
@@ -515,7 +515,7 @@
         <v>0.4373</v>
       </c>
       <c r="L2" t="n">
-        <v>0.147</v>
+        <v>0.2703</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>0.4373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1451</v>
+        <v>0.3033</v>
       </c>
     </row>
     <row r="4">
@@ -595,7 +595,7 @@
         <v>0.6982</v>
       </c>
       <c r="L4" t="n">
-        <v>0.027</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="5">
@@ -635,7 +635,7 @@
         <v>0.1688</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>-0.4534</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008</v>
+        <v>0.0012</v>
       </c>
     </row>
   </sheetData>
